--- a/banco.xlsx
+++ b/banco.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c050579\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7373A3A4-D6E0-40F7-8FB8-1BE4C9118CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7232C00F-1375-4F3F-BDEC-686CE6CAF939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados_Catálogo" sheetId="2" r:id="rId1"/>
+    <sheet name="Dados_Catalogo" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="BBTEC">Dados_Catálogo!$C$170:$C$180</definedName>
-    <definedName name="GIMI">Dados_Catálogo!$C$54:$C$75</definedName>
-    <definedName name="HB">Dados_Catálogo!$C$76:$C$86</definedName>
-    <definedName name="HELZIN">Dados_Catálogo!$C$181:$C$188</definedName>
-    <definedName name="MAXBARRAMENTOS">Dados_Catálogo!$C$156:$C$169</definedName>
-    <definedName name="MEGABARRE">Dados_Catálogo!$C$17:$C$53</definedName>
-    <definedName name="NOVEMP">Dados_Catálogo!$C$97:$C$111</definedName>
-    <definedName name="VEPAN">Dados_Catálogo!$C$133:$C$155</definedName>
-    <definedName name="WEG">Dados_Catálogo!$C$112:$C$132</definedName>
-    <definedName name="XBAR">Dados_Catálogo!$C$87:$C$96</definedName>
+    <definedName name="BBTEC">Dados_Catalogo!$C$170:$C$180</definedName>
+    <definedName name="GIMI">Dados_Catalogo!$C$54:$C$75</definedName>
+    <definedName name="HB">Dados_Catalogo!$C$76:$C$86</definedName>
+    <definedName name="HELZIN">Dados_Catalogo!$C$181:$C$188</definedName>
+    <definedName name="MAXBARRAMENTOS">Dados_Catalogo!$C$156:$C$169</definedName>
+    <definedName name="MEGABARRE">Dados_Catalogo!$C$17:$C$53</definedName>
+    <definedName name="NOVEMP">Dados_Catalogo!$C$97:$C$111</definedName>
+    <definedName name="VEPAN">Dados_Catalogo!$C$133:$C$155</definedName>
+    <definedName name="WEG">Dados_Catalogo!$C$112:$C$132</definedName>
+    <definedName name="XBAR">Dados_Catalogo!$C$87:$C$96</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -6546,6 +6546,44 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_dlc_DocIdUrl xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68">
+      <Url>https://copel0.sharepoint.com/sites/documentos-site-copel/_layouts/15/DocIdRedir.aspx?ID=536R5767CHC2-1361534186-16674</Url>
+      <Description>536R5767CHC2-1361534186-16674</Description>
+    </_dlc_DocIdUrl>
+    <_dlc_DocId xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68">536R5767CHC2-1361534186-16674</_dlc_DocId>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db302265-65a8-442b-80b8-c7550b891eda">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Respons_x00e1_vel xmlns="db302265-65a8-442b-80b8-c7550b891eda">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Respons_x00e1_vel>
+    <C_x00f3_digo xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
+    <TaxCatchAll xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
+    <_dlc_DocIdPersistId xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68" xsi:nil="true"/>
+    <Expiraem xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6595,7 +6633,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006189542E97E65E4E940E070C5A41C1E8" ma:contentTypeVersion="29" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="56de83ca40ff42f0108b52fc6f744c73">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="db302265-65a8-442b-80b8-c7550b891eda" xmlns:ns3="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc70fab0556f49e33f5b13b7c7d9ee3d" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6924,56 +6962,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_dlc_DocIdUrl xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68">
-      <Url>https://copel0.sharepoint.com/sites/documentos-site-copel/_layouts/15/DocIdRedir.aspx?ID=536R5767CHC2-1361534186-16674</Url>
-      <Description>536R5767CHC2-1361534186-16674</Description>
-    </_dlc_DocIdUrl>
-    <_dlc_DocId xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68">536R5767CHC2-1361534186-16674</_dlc_DocId>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db302265-65a8-442b-80b8-c7550b891eda">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Respons_x00e1_vel xmlns="db302265-65a8-442b-80b8-c7550b891eda">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Respons_x00e1_vel>
-    <C_x00f3_digo xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
-    <TaxCatchAll xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
-    <_dlc_DocIdPersistId xmlns="1454d0ca-2f96-4c88-b3bc-9b2c9d5f2c68" xsi:nil="true"/>
-    <Expiraem xmlns="db302265-65a8-442b-80b8-c7550b891eda" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78BBAD77-5F0C-490B-B16B-D94D56634DEE}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F92310-4219-4150-A26B-E367675E2F1D}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{181C9822-4D89-42F4-A6CA-11D0E1435D4A}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC10E0B-1140-4244-900B-AEAB45D07D86}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78BBAD77-5F0C-490B-B16B-D94D56634DEE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F92310-4219-4150-A26B-E367675E2F1D}"/>
 </file>